--- a/receipts/receipt_kova.xlsx
+++ b/receipts/receipt_kova.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,28 @@
         <v>160</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Stanley Adventure Mug</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Общая сумма</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>160</v>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>255</v>
       </c>
     </row>
   </sheetData>
